--- a/Posada_Colell_2007/Posada_Colell_2007_registry_rows.xlsx
+++ b/Posada_Colell_2007/Posada_Colell_2007_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Refc876fa4bf044b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rf5b029e321434148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rae14d70f07d14eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rdb3e192541244d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Re61d22f6865f44d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Ra207f9a5888e4921"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Mirror-guided behaviour and mark-test evidence in a gorilla</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Results / figures / tables: item selection pending</x:v>
+        <x:v>Table I: Gorilla ethogram frequencies and percentages across mirror/mark conditions</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap
@@ -350,13 +350,13 @@
         <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 4 / printed p. 579; original table uses Roman I. Single gorilla Xebo; retain covered, uncovered and uncovered-with-mark phases and their different exposure durations. Specific mark touches are also described in Results, PDF pp. 3–4.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/0628174989/Posada-2007-Another gorilla (Gorilla gorilla g.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Posada, S., &amp; Colell, M. (2007). Another gorilla (Gorilla gorilla gorilla) recognizes himself in a mirror. American Journal of Primatology, 69(5), 576–583. https://doi.org/10.1002/ajp.20355</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table I</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Posada_Colell_2007. Target: Results / figures / tables: item selection pending. Positive gorilla case study. Retain individual identity, habituation history and no-mirror baseline; assess the exact evidence against Suarez_Gallup_1981 and later methodological reviews. Do not extrapolate an individual success to a population rate.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 4 / printed p. 579; original table uses Roman I. Single gorilla Xebo; retain covered, uncovered and uncovered-with-mark phases and their different exposure durations. Specific mark touches are also described in Results, PDF pp. 3–4. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/0628174989/Posada-2007-Another gorilla (Gorilla gorilla g.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Mirror-guided behaviour and mark-test evidence in a gorilla</x:v>
+        <x:v>Gorilla ethogram frequencies and percentages across mirror/mark conditions</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -703,7 +705,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="100" customHeight="1">
@@ -711,7 +713,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -995,13 +997,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{602C35E7-8122-43AD-8F23-51A50106A61C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D75552CE-0D99-4A13-B4C9-A9D2B23A0943}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9912F29-5271-49EE-AF10-8F4ECDC028CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88F0200E-462C-403A-BB1F-894EEC1B98DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{620C58B6-1F77-44E4-81DB-0F08B76C538C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D65FDD41-9C99-42AB-90C7-118E4EECC465}"/>
 </file>